--- a/mx-simulator-lab/실습_워크북.xlsx
+++ b/mx-simulator-lab/실습_워크북.xlsx
@@ -19,6 +19,7 @@
     <sheet name="📝 시나리오문제" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="✅정답_수식" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="✅정답_숫자" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="📝 추가시나리오+정답" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +68,10 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -139,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -191,6 +196,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2378,6 +2395,342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>추가 실습 시나리오 + 정답 (전 이벤트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>중도해지 (회차/할인 조합별)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>위약금</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>사용분</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>할인회수</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>선납환불</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>등록비</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>24회차·전체할인</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>1,755,530</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>47,400</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>515,800</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>-2,394,500</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>29,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>37회차·선납할인+다품목</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>1,286,840</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>53,400</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>510,000</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>-1,755,200</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>45,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>48회차·전체할인</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>892,520</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>47,400</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>1,051,400</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>-1,217,400</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>59,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>37회차·선납할인+단품</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>1,286,840</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>53,000</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>535,300</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>-1,755,200</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>45,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>중도완납 (30회차·선납+선납할인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>완납금</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>사용분</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>선납차감</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>금액(원)</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>6,268,700</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>59,400</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>-2,098,200</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr"/>
+      <c r="F12" s="19" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>AS 미사용 보상 (기본구독료 163,300 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>미사용일/그달일</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>보상금</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>20일 / 31일</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>105,400</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr"/>
+      <c r="D16" s="19" t="inlineStr"/>
+      <c r="E16" s="19" t="inlineStr"/>
+      <c r="F16" s="19" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>10일 / 30일</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>54,500</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="21" t="inlineStr"/>
+      <c r="E17" s="21" t="inlineStr"/>
+      <c r="F17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>31일 / 31일(한달)</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>163,300</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr"/>
+      <c r="D18" s="19" t="inlineStr"/>
+      <c r="E18" s="19" t="inlineStr"/>
+      <c r="F18" s="19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>※ 직접 풀어보고 위 정답과 대조하세요. 계산기(simulator-qa.html)에서도 같은 값 확인 가능.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
